--- a/간이지급명세서_2026-02.xlsx
+++ b/간이지급명세서_2026-02.xlsx
@@ -438,8 +438,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -532,12 +532,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>김</t>
+          <t>김건영</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>860310-1330000</t>
+          <t>610126-2017237</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -574,35 +574,787 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>940902</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>김경옥</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>600824-2036112</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>940902</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>김현주</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>701122-2000113</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>940902</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>김호준</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>990211-1074515</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>940909</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>이땡땡</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>860310-1330000</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>350000</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>10500</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>1050</v>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>노연희</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>671113-2670818</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>940902</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>박상미</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>720805-2621623</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>940909</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>박선영</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>781231-2541310</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>160000</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>940909</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>배정호</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>760103-1036314</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>940909</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>성영심</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>630801-2019718</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>940902</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>신경숙</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>600815-2009743</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>280000</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>8400</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>940909</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>안용언</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>620201-1063211</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>940902</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>윤지원</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>740710-2006111</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>160000</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>940902</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>이현주</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>730905-2025026</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>160000</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>940909</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>장용아</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>901207-2056514</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>940909</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>전이부</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>721015-2545624</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>940902</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>주혜민</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>710626-2001818</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>940902</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>최강호</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>560316-2068518</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>940909</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>함숙자</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>750129-2053015</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
